--- a/Excel_files/fig6.xlsx
+++ b/Excel_files/fig6.xlsx
@@ -5,18 +5,19 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Neu" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="rockon.smu" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="synapse2.smu" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="synapse.smu" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="cs_g" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="cs_E" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="cs_FAT" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="es" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="noise" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Neu" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="rockon.smu" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="synapse2.smu" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="synapse.smu" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="depol.smu" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="cs_g" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="cs_E" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="cs_FAT" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="es" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="noise" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="179">
   <si>
     <t xml:space="preserve">File</t>
   </si>
@@ -1315,767 +1316,767 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="24" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="24" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="25" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="25" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="28" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="28" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="29" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="29" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="32" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="32" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="36" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="36" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="32" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="32" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="38" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="38" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="39" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="39" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="41" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="41" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="42" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="42" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="43" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="43" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="14" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="57" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="58" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="59" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="59" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="60" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="60" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="61" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="61" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="62" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="62" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="63" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="63" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="64" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="64" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="65" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="65" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="66" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="66" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="67" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="67" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="68" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="68" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="43" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="43" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="48" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="48" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="25" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="25" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4362,14 +4363,14 @@
     <xdr:from>
       <xdr:col>36</xdr:col>
       <xdr:colOff>93240</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>4680</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>177120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
-      <xdr:colOff>44640</xdr:colOff>
+      <xdr:colOff>43560</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4378,8 +4379,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20980800" y="928440"/>
-          <a:ext cx="2399400" cy="279000"/>
+          <a:off x="18895680" y="928440"/>
+          <a:ext cx="2154240" cy="279000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4411,6 +4412,7 @@
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Cambria Math"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
             <a:t>𝑑𝐴𝑡</a:t>
           </a:r>
@@ -4420,6 +4422,7 @@
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Cambria Math"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:rPr>
             <a:t>/𝑑𝑡=(𝑋𝑡 −(𝑢_1+𝑢_2 )(𝑑𝐴𝑡⁄𝑑𝑡)−𝐴𝑡)/(𝑢_1 𝑢_2 )</a:t>
           </a:r>
@@ -4434,13 +4437,119 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:KQ62"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="9.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.45"/>
@@ -4950,7 +5059,7 @@
       <c r="KP1" s="14"/>
       <c r="KQ1" s="14"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E2" s="15" t="s">
         <v>13</v>
       </c>
@@ -5319,7 +5428,7 @@
       <c r="KP2" s="18"/>
       <c r="KQ2" s="18"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="20" t="s">
         <v>16</v>
       </c>
@@ -6227,7 +6336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="str">
         <f aca="false">Neu!B4</f>
         <v>A</v>
@@ -6609,7 +6718,7 @@
       <c r="KP4" s="41"/>
       <c r="KQ4" s="45"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="str">
         <f aca="false">Neu!B5</f>
         <v>B</v>
@@ -7297,7 +7406,7 @@
       <c r="KP6" s="41"/>
       <c r="KQ6" s="45"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32" t="n">
         <f aca="false">Neu!B7</f>
         <v>0</v>
@@ -7605,7 +7714,7 @@
       <c r="KP7" s="41"/>
       <c r="KQ7" s="45"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="n">
         <f aca="false">Neu!B8</f>
         <v>0</v>
@@ -7913,7 +8022,7 @@
       <c r="KP8" s="41"/>
       <c r="KQ8" s="45"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="n">
         <f aca="false">Neu!B9</f>
         <v>0</v>
@@ -8221,7 +8330,7 @@
       <c r="KP9" s="41"/>
       <c r="KQ9" s="45"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="n">
         <f aca="false">Neu!B10</f>
         <v>0</v>
@@ -8529,7 +8638,7 @@
       <c r="KP10" s="41"/>
       <c r="KQ10" s="45"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="32" t="n">
         <f aca="false">Neu!B11</f>
         <v>0</v>
@@ -8837,7 +8946,7 @@
       <c r="KP11" s="41"/>
       <c r="KQ11" s="45"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="n">
         <f aca="false">Neu!B12</f>
         <v>0</v>
@@ -9145,7 +9254,7 @@
       <c r="KP12" s="41"/>
       <c r="KQ12" s="45"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="n">
         <f aca="false">Neu!B13</f>
         <v>0</v>
@@ -9453,7 +9562,7 @@
       <c r="KP13" s="41"/>
       <c r="KQ13" s="45"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="n">
         <f aca="false">Neu!B14</f>
         <v>0</v>
@@ -9761,7 +9870,7 @@
       <c r="KP14" s="41"/>
       <c r="KQ14" s="45"/>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="n">
         <f aca="false">Neu!B15</f>
         <v>0</v>
@@ -10069,7 +10178,7 @@
       <c r="KP15" s="41"/>
       <c r="KQ15" s="45"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="n">
         <f aca="false">Neu!B16</f>
         <v>0</v>
@@ -10377,7 +10486,7 @@
       <c r="KP16" s="41"/>
       <c r="KQ16" s="45"/>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="n">
         <f aca="false">Neu!B17</f>
         <v>0</v>
@@ -10685,7 +10794,7 @@
       <c r="KP17" s="41"/>
       <c r="KQ17" s="45"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="n">
         <f aca="false">Neu!B18</f>
         <v>0</v>
@@ -10993,7 +11102,7 @@
       <c r="KP18" s="41"/>
       <c r="KQ18" s="45"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="n">
         <f aca="false">Neu!B19</f>
         <v>0</v>
@@ -11301,7 +11410,7 @@
       <c r="KP19" s="41"/>
       <c r="KQ19" s="45"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="n">
         <f aca="false">Neu!B20</f>
         <v>0</v>
@@ -11609,7 +11718,7 @@
       <c r="KP20" s="41"/>
       <c r="KQ20" s="45"/>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="n">
         <f aca="false">Neu!B21</f>
         <v>0</v>
@@ -11917,7 +12026,7 @@
       <c r="KP21" s="41"/>
       <c r="KQ21" s="45"/>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="32" t="n">
         <f aca="false">Neu!B22</f>
         <v>0</v>
@@ -12225,7 +12334,7 @@
       <c r="KP22" s="41"/>
       <c r="KQ22" s="45"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="n">
         <f aca="false">Neu!B23</f>
         <v>0</v>
@@ -12533,7 +12642,7 @@
       <c r="KP23" s="41"/>
       <c r="KQ23" s="45"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="32" t="n">
         <f aca="false">Neu!B24</f>
         <v>0</v>
@@ -12841,7 +12950,7 @@
       <c r="KP24" s="54"/>
       <c r="KQ24" s="55"/>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="61"/>
       <c r="D25" s="62"/>
       <c r="E25" s="62"/>
@@ -13110,7 +13219,7 @@
       <c r="JC25" s="62"/>
       <c r="JD25" s="62"/>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="62"/>
       <c r="E26" s="62"/>
       <c r="G26" s="62"/>
@@ -13391,7 +13500,7 @@
       <c r="JC26" s="62"/>
       <c r="JD26" s="62"/>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="62"/>
       <c r="E27" s="62"/>
       <c r="G27" s="62"/>
@@ -13770,7 +13879,7 @@
       <c r="EG28" s="62"/>
       <c r="EH28" s="62"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="65" t="s">
         <v>34</v>
       </c>
@@ -13809,7 +13918,7 @@
       <c r="EH29" s="62"/>
       <c r="HO29" s="62"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="66" t="s">
         <v>16</v>
       </c>
@@ -13972,7 +14081,7 @@
       <c r="DV30" s="62"/>
       <c r="HO30" s="62"/>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="71"/>
       <c r="E31" s="44"/>
       <c r="F31" s="41"/>
@@ -14039,7 +14148,7 @@
       <c r="DV31" s="62"/>
       <c r="HO31" s="62"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="74"/>
       <c r="E32" s="44"/>
       <c r="F32" s="41"/>
@@ -14105,7 +14214,7 @@
       <c r="DU32" s="62"/>
       <c r="DV32" s="62"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="74"/>
       <c r="E33" s="44"/>
       <c r="F33" s="41"/>
@@ -14171,7 +14280,7 @@
       <c r="DU33" s="62"/>
       <c r="DV33" s="62"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="74"/>
       <c r="E34" s="40"/>
       <c r="F34" s="41"/>
@@ -14229,7 +14338,7 @@
       </c>
       <c r="BE34" s="40"/>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="74" t="n">
         <f aca="false">Neu!$B8</f>
         <v>0</v>
@@ -14293,7 +14402,7 @@
       </c>
       <c r="BE35" s="40"/>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="74" t="n">
         <f aca="false">Neu!$B9</f>
         <v>0</v>
@@ -14357,7 +14466,7 @@
       </c>
       <c r="BE36" s="40"/>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="74" t="n">
         <f aca="false">Neu!$B10</f>
         <v>0</v>
@@ -14421,7 +14530,7 @@
       </c>
       <c r="BE37" s="40"/>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="74" t="n">
         <f aca="false">Neu!$B11</f>
         <v>0</v>
@@ -14485,7 +14594,7 @@
       </c>
       <c r="BE38" s="40"/>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D39" s="74" t="n">
         <f aca="false">Neu!$B12</f>
         <v>0</v>
@@ -14549,7 +14658,7 @@
       </c>
       <c r="BE39" s="40"/>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="74" t="n">
         <f aca="false">Neu!$B13</f>
         <v>0</v>
@@ -14613,7 +14722,7 @@
       </c>
       <c r="BE40" s="40"/>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="74" t="n">
         <f aca="false">Neu!$B14</f>
         <v>0</v>
@@ -14677,7 +14786,7 @@
       </c>
       <c r="BE41" s="40"/>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="74" t="n">
         <f aca="false">Neu!$B15</f>
         <v>0</v>
@@ -14741,7 +14850,7 @@
       </c>
       <c r="BE42" s="40"/>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D43" s="74" t="n">
         <f aca="false">Neu!$B16</f>
         <v>0</v>
@@ -14805,7 +14914,7 @@
       </c>
       <c r="BE43" s="40"/>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="74" t="n">
         <f aca="false">Neu!$B17</f>
         <v>0</v>
@@ -14869,7 +14978,7 @@
       </c>
       <c r="BE44" s="40"/>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="74" t="n">
         <f aca="false">Neu!$B18</f>
         <v>0</v>
@@ -14933,7 +15042,7 @@
       </c>
       <c r="BE45" s="40"/>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="74" t="n">
         <f aca="false">Neu!$B19</f>
         <v>0</v>
@@ -14997,7 +15106,7 @@
       </c>
       <c r="BE46" s="40"/>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="74" t="n">
         <f aca="false">Neu!$B20</f>
         <v>0</v>
@@ -15061,7 +15170,7 @@
       </c>
       <c r="BE47" s="40"/>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="74" t="n">
         <f aca="false">Neu!$B21</f>
         <v>0</v>
@@ -15125,7 +15234,7 @@
       </c>
       <c r="BE48" s="40"/>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="74" t="n">
         <f aca="false">Neu!$B22</f>
         <v>0</v>
@@ -15189,7 +15298,7 @@
       </c>
       <c r="BE49" s="40"/>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="74" t="n">
         <f aca="false">Neu!$B23</f>
         <v>0</v>
@@ -15253,7 +15362,7 @@
       </c>
       <c r="BE50" s="40"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="76" t="n">
         <f aca="false">Neu!$B24</f>
         <v>0</v>
@@ -15820,13 +15929,93 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="188" width="35.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="189" width="10.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="189" width="9.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="189" width="17.17"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="189" width="9.18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="190"/>
+      <c r="B1" s="191" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="191" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="191" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="190" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="72" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" s="72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="190" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="72" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" s="72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="190" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="72" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z87"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="62" width="8.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="62" width="10.54"/>
@@ -15919,7 +16108,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="84" t="s">
         <v>92</v>
       </c>
@@ -16042,7 +16231,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="88" t="s">
         <v>123</v>
       </c>
@@ -16056,7 +16245,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="89" t="s">
         <v>127</v>
       </c>
@@ -16631,7 +16820,7 @@
       <c r="Y22" s="41"/>
       <c r="Z22" s="45"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="98"/>
       <c r="B23" s="99"/>
       <c r="C23" s="54"/>
@@ -17663,12 +17852,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z87"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="62" width="8.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="62" width="10.54"/>
@@ -17761,7 +17950,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="84" t="s">
         <v>92</v>
       </c>
@@ -17884,7 +18073,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="88" t="s">
         <v>123</v>
       </c>
@@ -17898,7 +18087,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="89" t="s">
         <v>127</v>
       </c>
@@ -18473,7 +18662,7 @@
       <c r="Y22" s="41"/>
       <c r="Z22" s="45"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="98"/>
       <c r="B23" s="99"/>
       <c r="C23" s="54"/>
@@ -19505,12 +19694,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z87"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="62" width="8.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="62" width="10.54"/>
@@ -19603,7 +19792,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="84" t="s">
         <v>92</v>
       </c>
@@ -19726,7 +19915,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="88" t="s">
         <v>123</v>
       </c>
@@ -19740,7 +19929,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="89" t="s">
         <v>127</v>
       </c>
@@ -20315,7 +20504,7 @@
       <c r="Y22" s="41"/>
       <c r="Z22" s="45"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="98"/>
       <c r="B23" s="99"/>
       <c r="C23" s="54"/>
@@ -21339,12 +21528,1846 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Z87"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="62" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="62" width="10.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="62" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="62" width="10.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="62" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="62" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="62" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="62" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="62" width="10.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="62" width="12.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="62" width="19.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="62" width="10.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="62" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="62" width="10.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="62" width="9.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="62" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="62" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="62" width="10.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="62" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="62" width="17.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="62" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="62" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="62" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="62" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="28" style="62" width="7.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="32" style="62" width="9.18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F1" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" s="82" t="s">
+        <v>78</v>
+      </c>
+      <c r="T1" s="82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" s="82" t="s">
+        <v>89</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="U2" s="62" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="84" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="82" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="N3" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="R3" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="U3" s="62" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="41" t="n">
+        <v>5E-005</v>
+      </c>
+      <c r="D4" s="84" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="86" t="s">
+        <v>109</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="R4" s="82" t="s">
+        <v>112</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="U4" s="62" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="87" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="82" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="62" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="88" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="86" t="s">
+        <v>124</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="N6" s="82" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="92" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="93" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="T8" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="U8" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="V8" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="W8" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="X8" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y8" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z8" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="41" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J9" s="41" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K9" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="44"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="41"/>
+      <c r="Z9" s="45"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="95" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="96" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="41" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J10" s="41" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K10" s="96" t="s">
+        <v>143</v>
+      </c>
+      <c r="L10" s="44"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="96"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="95" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="96" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="41" t="n">
+        <v>-90</v>
+      </c>
+      <c r="J11" s="41" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K11" s="96" t="s">
+        <v>145</v>
+      </c>
+      <c r="L11" s="44"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="96"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41"/>
+      <c r="Z11" s="45"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="96"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="96"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="41"/>
+      <c r="U13" s="96"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="41"/>
+      <c r="X13" s="41"/>
+      <c r="Y13" s="41"/>
+      <c r="Z13" s="96"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="41"/>
+      <c r="Y14" s="41"/>
+      <c r="Z14" s="96"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="45"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="45"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="45"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="45"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="41"/>
+      <c r="Y17" s="41"/>
+      <c r="Z17" s="45"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="45"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="41"/>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="94"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="45"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="41"/>
+      <c r="Z19" s="45"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="94"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="45"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="45"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="94"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="45"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="94"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="45"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="45"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="55"/>
+      <c r="V23" s="52"/>
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="55"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="L25" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="M25" s="81"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="G26" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="L26" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="M26" s="101" t="s">
+        <v>151</v>
+      </c>
+      <c r="N26" s="101"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="101"/>
+      <c r="Q26" s="101"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="L27" s="44"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="101"/>
+      <c r="Q27" s="101"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="41"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="41"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41"/>
+      <c r="J59" s="41"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="41"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="41"/>
+      <c r="J61" s="41"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="41"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="41"/>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
+      <c r="J65" s="41"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
+      <c r="J66" s="41"/>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="41"/>
+      <c r="J67" s="41"/>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="41"/>
+      <c r="J68" s="41"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="41"/>
+      <c r="J69" s="41"/>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="41"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="41"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="41"/>
+      <c r="J72" s="41"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="41"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="41"/>
+      <c r="I73" s="41"/>
+      <c r="J73" s="41"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="41"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="41"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="41"/>
+      <c r="I74" s="41"/>
+      <c r="J74" s="41"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
+      <c r="J75" s="41"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="41"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="41"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="41"/>
+      <c r="J76" s="41"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="41"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="41"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="41"/>
+      <c r="I77" s="41"/>
+      <c r="J77" s="41"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="41"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
+      <c r="J78" s="41"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
+      <c r="J79" s="41"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
+      <c r="J80" s="41"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="41"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="41"/>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="41"/>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="41"/>
+      <c r="J84" s="41"/>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="41"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="41"/>
+      <c r="J85" s="41"/>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="41"/>
+      <c r="J86" s="41"/>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="41"/>
+      <c r="J87" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="V7:Z7"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="M26:Q27"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="cellIs" priority="2" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="178">
+      <formula>MAX($E$9:$E$23)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="179">
+      <formula>LEN(TRIM(H14))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="180">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14:H15">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="181">
+      <formula>LEN(TRIM(H14))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="182">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H16">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="183">
+      <formula>LEN(TRIM(H15))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="184">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16:H17">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="185">
+      <formula>LEN(TRIM(H16))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="186">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="187">
+      <formula>LEN(TRIM(H17))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="188">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="189">
+      <formula>LEN(TRIM(H18))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="190">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M9">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="191">
+      <formula>LEN(TRIM(M9))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="192">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="193">
+      <formula>LEN(TRIM(M9))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="194">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="195">
+      <formula>LEN(TRIM(M11))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="196">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M12">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="197">
+      <formula>LEN(TRIM(M11))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="198">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M12">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="199">
+      <formula>LEN(TRIM(M12))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="200">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="201">
+      <formula>LEN(TRIM(M12))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="202">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="203">
+      <formula>LEN(TRIM(M12))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="204">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M13">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="205">
+      <formula>LEN(TRIM(M13))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="206">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M13:M14">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="207">
+      <formula>LEN(TRIM(M13))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="208">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M14:M15">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="209">
+      <formula>LEN(TRIM(M14))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="210">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M15:M16">
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="211">
+      <formula>LEN(TRIM(M15))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="212">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M16:M17">
+    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="213">
+      <formula>LEN(TRIM(M16))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="214">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M17:M18">
+    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="215">
+      <formula>LEN(TRIM(M17))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="40" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="216">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18">
+    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="217">
+      <formula>LEN(TRIM(M18))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="218">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R10">
+    <cfRule type="expression" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="219">
+      <formula>LEN(TRIM(R10))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="220">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R10:R11">
+    <cfRule type="expression" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="221">
+      <formula>LEN(TRIM(R10))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="46" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="222">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R11:R12">
+    <cfRule type="expression" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="223">
+      <formula>LEN(TRIM(R11))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="48" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="224">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R12">
+    <cfRule type="expression" priority="49" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="225">
+      <formula>LEN(TRIM(R12))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="50" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="226">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="227">
+      <formula>LEN(TRIM(R12))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="228">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="53" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="229">
+      <formula>LEN(TRIM(R12))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="230">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R13">
+    <cfRule type="expression" priority="55" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="231">
+      <formula>LEN(TRIM(R13))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="56" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="232">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R13:R14">
+    <cfRule type="expression" priority="57" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="233">
+      <formula>LEN(TRIM(R13))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="58" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="234">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R14">
+    <cfRule type="expression" priority="59" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="235">
+      <formula>LEN(TRIM(R14))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="60" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="236">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W10">
+    <cfRule type="expression" priority="61" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="237">
+      <formula>LEN(TRIM(W10))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="62" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="238">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="239">
+      <formula>LEN(TRIM(W10))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="64" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="240">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W13:W14">
+    <cfRule type="expression" priority="65" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="241">
+      <formula>LEN(TRIM(W13))=0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="66" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="242">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F9:F23 K9:K23 P9:P23 U9:U23 Z9:Z23" type="list">
+      <formula1>"green,red,yellow,blue,orange,cyan,black,white,magenta"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AD76"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="102" width="4.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="102" width="9.18"/>
@@ -21352,7 +23375,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="24" style="102" width="9.18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="103"/>
       <c r="B1" s="103"/>
       <c r="C1" s="104" t="s">
@@ -21379,7 +23402,7 @@
       <c r="V1" s="104"/>
       <c r="W1" s="104"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="103"/>
       <c r="B2" s="103"/>
       <c r="C2" s="105" t="str">
@@ -23983,13 +26006,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AD76"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="102" width="4.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="102" width="9.18"/>
@@ -23997,7 +26020,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="24" style="102" width="9.18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="103"/>
       <c r="B1" s="103"/>
       <c r="C1" s="104" t="s">
@@ -24024,7 +26047,7 @@
       <c r="V1" s="104"/>
       <c r="W1" s="104"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="103"/>
       <c r="B2" s="103"/>
       <c r="C2" s="105" t="str">
@@ -26660,13 +28683,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AL229"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="102" width="4.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="102" width="9.18"/>
@@ -26684,7 +28707,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="37" style="102" width="9.18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="103"/>
       <c r="B1" s="103"/>
       <c r="C1" s="104" t="s">
@@ -26729,7 +28752,7 @@
       </c>
       <c r="AJ1" s="154"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="103"/>
       <c r="B2" s="103"/>
       <c r="C2" s="105" t="str">
@@ -29495,7 +31518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CC6CD91A-3E65-496F-81C8-7BE2E870762B}</x14:id>
+          <x14:id>{7592C07A-BBD0-45F2-A088-34A060CAD230}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -29524,7 +31547,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CC6CD91A-3E65-496F-81C8-7BE2E870762B}">
+          <x14:cfRule type="dataBar" id="{7592C07A-BBD0-45F2-A088-34A060CAD230}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="false">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -29540,13 +31563,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.18359375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.18"/>
@@ -29555,7 +31578,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="26" style="1" width="9.18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="165"/>
       <c r="B1" s="165"/>
       <c r="C1" s="166" t="s">
@@ -29576,7 +31599,7 @@
       <c r="P1" s="166"/>
       <c r="Q1" s="166"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="165"/>
       <c r="B2" s="165"/>
       <c r="C2" s="167" t="str">
@@ -30931,84 +32954,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="188" width="35.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="189" width="10.82"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="189" width="9.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="189" width="17.17"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="189" width="9.18"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="190"/>
-      <c r="B1" s="191" t="s">
-        <v>173</v>
-      </c>
-      <c r="C1" s="191" t="s">
-        <v>174</v>
-      </c>
-      <c r="D1" s="191" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="190" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="72" t="n">
-        <v>200</v>
-      </c>
-      <c r="D2" s="72" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="190" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="72" t="n">
-        <v>200</v>
-      </c>
-      <c r="D3" s="72" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="190" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="72" t="n">
-        <v>200</v>
-      </c>
-      <c r="D4" s="72" t="n">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>